--- a/sd-hub-translations.xlsx
+++ b/sd-hub-translations.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\NEO\extensions\sd-hub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0283077B-63AC-49BD-ADFE-18E48B208D92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0A47FB9-5221-4D70-92BC-010B45D76AF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{3ED67704-AF6D-45B2-B79F-70598EE793EA}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="905" uniqueCount="873">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="911" uniqueCount="874">
   <si>
     <t>Key</t>
   </si>
@@ -2639,6 +2639,9 @@
   </si>
   <si>
     <t>&lt;br&gt;&lt;strong&gt;Huggingface 토큰&lt;/strong&gt; &lt;strong&gt;WRITE&lt;/strong&gt; 권한 을 &lt;a href="https://huggingface.co/settings/tokens" class="sdhub-link" target="_blank"&gt;여기&lt;/a&gt;에서 받으세요.&lt;br&gt;사용법은 &lt;a href="https://github.com/gutris1/sd-hub/blob/master/README.md#uploader" class="sdhub-link" target="_blank"&gt;여기&lt;/a&gt;에서 확인하세요.&lt;br&gt;</t>
+  </si>
+  <si>
+    <t>cancel_download</t>
   </si>
 </sst>
 </file>
@@ -3537,7 +3540,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{780E0960-BCEF-42B8-BB82-3303C65E8F3F}">
-  <dimension ref="A1:F180"/>
+  <dimension ref="A1:F181"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36" style="4" bestFit="1" customWidth="1"/>
@@ -4106,839 +4109,839 @@
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="B35" t="s">
-        <v>147</v>
-      </c>
-      <c r="C35" t="s">
-        <v>148</v>
-      </c>
-      <c r="D35" t="s">
-        <v>149</v>
-      </c>
-      <c r="E35" t="s">
-        <v>150</v>
-      </c>
-      <c r="F35" t="s">
-        <v>151</v>
+      <c r="A35" s="3" t="s">
+        <v>873</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>651</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>658</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>659</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>659</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>666</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="B36" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="C36" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="D36" t="s">
-        <v>155</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>156</v>
+        <v>149</v>
+      </c>
+      <c r="E36" t="s">
+        <v>150</v>
       </c>
       <c r="F36" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="B37" t="s">
+        <v>153</v>
+      </c>
+      <c r="C37" t="s">
+        <v>154</v>
+      </c>
+      <c r="D37" t="s">
+        <v>155</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="F37" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="4" t="s">
         <v>857</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="B38" s="1" t="s">
         <v>858</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C38" s="1" t="s">
         <v>859</v>
       </c>
-      <c r="D37" s="1" t="s">
+      <c r="D38" s="1" t="s">
         <v>860</v>
       </c>
-      <c r="E37" s="2" t="s">
+      <c r="E38" s="2" t="s">
         <v>861</v>
       </c>
-      <c r="F37" s="1" t="s">
+      <c r="F38" s="1" t="s">
         <v>862</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E38" s="2"/>
-    </row>
-    <row r="39" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="11" t="s">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E39" s="2"/>
+    </row>
+    <row r="40" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="11" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="4" t="s">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B41" t="s">
         <v>191</v>
       </c>
-      <c r="C40" t="s">
+      <c r="C41" t="s">
         <v>192</v>
       </c>
-      <c r="D40" t="s">
+      <c r="D41" t="s">
         <v>193</v>
       </c>
-      <c r="E40" t="s">
+      <c r="E41" t="s">
         <v>194</v>
       </c>
-      <c r="F40" t="s">
+      <c r="F41" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="3" t="s">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="B42" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="C42" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="D41" s="1" t="s">
+      <c r="D42" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="E41" t="s">
+      <c r="E42" t="s">
         <v>328</v>
       </c>
-      <c r="F41" t="s">
+      <c r="F42" t="s">
         <v>329</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="F42" s="2" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="B48" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C47" s="2" t="s">
+      <c r="C48" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D47" s="2" t="s">
+      <c r="D48" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E47" s="2" t="s">
+      <c r="E48" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="F47" s="2" t="s">
+      <c r="F48" s="2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="5"/>
-      <c r="B48" s="2"/>
-      <c r="C48" s="2"/>
-      <c r="D48" s="2"/>
-      <c r="E48" s="2"/>
-      <c r="F48" s="2"/>
-    </row>
-    <row r="49" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="11" t="s">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="5"/>
+      <c r="B49" s="2"/>
+      <c r="C49" s="2"/>
+      <c r="D49" s="2"/>
+      <c r="E49" s="2"/>
+      <c r="F49" s="2"/>
+    </row>
+    <row r="50" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="11" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="5" t="s">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="B50" s="2" t="s">
+      <c r="B51" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="C50" s="2" t="s">
+      <c r="C51" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="D50" s="2" t="s">
+      <c r="D51" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="E50" s="2" t="s">
+      <c r="E51" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="F50" s="2" t="s">
+      <c r="F51" s="2" t="s">
         <v>238</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="F51" s="2" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="B52" s="2" t="s">
+      <c r="B53" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="C52" s="2" t="s">
+      <c r="C53" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="D52" s="2" t="s">
+      <c r="D53" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="E52" s="2" t="s">
+      <c r="E53" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="F52" s="2" t="s">
+      <c r="F53" s="2" t="s">
         <v>250</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="F53" s="2" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>163</v>
+        <v>252</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>164</v>
+        <v>253</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>414</v>
+        <v>254</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>415</v>
+        <v>255</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>167</v>
+        <v>256</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
-        <v>293</v>
+        <v>257</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>408</v>
+        <v>163</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>410</v>
+        <v>164</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>413</v>
+        <v>167</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
-        <v>258</v>
+        <v>293</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>259</v>
+        <v>408</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>260</v>
+        <v>410</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>261</v>
+        <v>411</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>261</v>
+        <v>412</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>262</v>
+        <v>413</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>409</v>
+        <v>288</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>416</v>
+        <v>289</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>417</v>
+        <v>290</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>417</v>
+        <v>291</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>418</v>
+        <v>292</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="B63" s="2" t="s">
+      <c r="B64" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="C63" s="2" t="s">
+      <c r="C64" s="2" t="s">
         <v>419</v>
       </c>
-      <c r="D63" s="2" t="s">
+      <c r="D64" s="2" t="s">
         <v>420</v>
       </c>
-      <c r="E63" s="2" t="s">
+      <c r="E64" s="2" t="s">
         <v>420</v>
       </c>
-      <c r="F63" s="2" t="s">
+      <c r="F64" s="2" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" s="5"/>
-      <c r="B64" s="2"/>
-      <c r="C64" s="2"/>
-      <c r="D64" s="2"/>
-      <c r="E64" s="2"/>
-      <c r="F64" s="2"/>
-    </row>
-    <row r="65" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66" s="3" t="s">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" s="5"/>
+      <c r="B65" s="2"/>
+      <c r="C65" s="2"/>
+      <c r="D65" s="2"/>
+      <c r="E65" s="2"/>
+      <c r="F65" s="2"/>
+    </row>
+    <row r="66" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="B66" s="1" t="s">
+      <c r="B67" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="C66" t="s">
+      <c r="C67" t="s">
         <v>313</v>
       </c>
-      <c r="D66" t="s">
+      <c r="D67" t="s">
         <v>314</v>
       </c>
-      <c r="E66" t="s">
+      <c r="E67" t="s">
         <v>315</v>
       </c>
-      <c r="F66" t="s">
+      <c r="F67" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A67" s="4" t="s">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" s="4" t="s">
         <v>317</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B68" t="s">
         <v>318</v>
       </c>
-      <c r="C67" t="s">
+      <c r="C68" t="s">
         <v>319</v>
       </c>
-      <c r="D67" t="s">
+      <c r="D68" t="s">
         <v>320</v>
       </c>
-      <c r="E67" t="s">
+      <c r="E68" t="s">
         <v>321</v>
       </c>
-      <c r="F67" t="s">
+      <c r="F68" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="69" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="11" t="s">
+    <row r="70" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="11" t="s">
         <v>335</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A70" s="4" t="s">
-        <v>323</v>
-      </c>
-      <c r="B70" s="8" t="s">
-        <v>863</v>
-      </c>
-      <c r="C70" t="s">
-        <v>864</v>
-      </c>
-      <c r="D70" t="s">
-        <v>865</v>
-      </c>
-      <c r="E70" t="s">
-        <v>866</v>
-      </c>
-      <c r="F70" t="s">
-        <v>867</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
-        <v>324</v>
-      </c>
-      <c r="B71" t="s">
-        <v>868</v>
+        <v>323</v>
+      </c>
+      <c r="B71" s="8" t="s">
+        <v>863</v>
       </c>
       <c r="C71" t="s">
-        <v>869</v>
+        <v>864</v>
       </c>
       <c r="D71" t="s">
-        <v>870</v>
+        <v>865</v>
       </c>
       <c r="E71" t="s">
-        <v>871</v>
+        <v>866</v>
       </c>
       <c r="F71" t="s">
-        <v>872</v>
+        <v>867</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="B72" t="s">
+        <v>868</v>
+      </c>
+      <c r="C72" t="s">
+        <v>869</v>
+      </c>
+      <c r="D72" t="s">
+        <v>870</v>
+      </c>
+      <c r="E72" t="s">
+        <v>871</v>
+      </c>
+      <c r="F72" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A73" s="4" t="s">
         <v>325</v>
       </c>
-      <c r="B72" s="9" t="s">
+      <c r="B73" s="9" t="s">
         <v>422</v>
       </c>
-      <c r="C72" t="s">
+      <c r="C73" t="s">
         <v>423</v>
       </c>
-      <c r="D72" t="s">
+      <c r="D73" t="s">
         <v>424</v>
       </c>
-      <c r="E72" t="s">
+      <c r="E73" t="s">
         <v>425</v>
       </c>
-      <c r="F72" t="s">
+      <c r="F73" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B73" s="9"/>
-    </row>
-    <row r="74" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="12" t="s">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B74" s="9"/>
+    </row>
+    <row r="75" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="12" t="s">
         <v>297</v>
       </c>
-      <c r="B74" s="12"/>
-      <c r="C74" s="12"/>
-      <c r="D74" s="12"/>
-      <c r="E74" s="12"/>
-      <c r="F74" s="12"/>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A75" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D75" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E75" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F75" s="1" t="s">
-        <v>11</v>
-      </c>
+      <c r="B75" s="12"/>
+      <c r="C75" s="12"/>
+      <c r="D75" s="12"/>
+      <c r="E75" s="12"/>
+      <c r="F75" s="12"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
-        <v>141</v>
+        <v>30</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>144</v>
+        <v>31</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
-        <v>41</v>
+        <v>142</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>333</v>
+        <v>143</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>46</v>
+        <v>333</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>47</v>
@@ -4955,1718 +4958,1738 @@
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
-        <v>402</v>
+        <v>64</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="C87" t="s">
-        <v>404</v>
-      </c>
-      <c r="D87" t="s">
-        <v>405</v>
-      </c>
-      <c r="E87" t="s">
-        <v>406</v>
-      </c>
-      <c r="F87" t="s">
-        <v>407</v>
+        <v>65</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
-        <v>76</v>
+        <v>402</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C88" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="D88" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="E88" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="F88" s="1" t="s">
-        <v>81</v>
+        <v>403</v>
+      </c>
+      <c r="C88" t="s">
+        <v>404</v>
+      </c>
+      <c r="D88" t="s">
+        <v>405</v>
+      </c>
+      <c r="E88" t="s">
+        <v>406</v>
+      </c>
+      <c r="F88" t="s">
+        <v>407</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
-        <v>628</v>
+        <v>88</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>791</v>
+        <v>89</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>633</v>
+        <v>90</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>634</v>
+        <v>91</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>636</v>
+        <v>92</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>630</v>
+        <v>93</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
-        <v>789</v>
+        <v>628</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>799</v>
+        <v>633</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>800</v>
+        <v>634</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>801</v>
+        <v>636</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>802</v>
+        <v>630</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
-        <v>629</v>
+        <v>789</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>632</v>
+        <v>799</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>635</v>
+        <v>800</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>637</v>
+        <v>801</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>631</v>
+        <v>802</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
-        <v>788</v>
+        <v>629</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>803</v>
+        <v>632</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>804</v>
+        <v>635</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>805</v>
+        <v>637</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>806</v>
+        <v>631</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
+        <v>788</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>793</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>803</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>804</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>805</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A96" s="3" t="s">
         <v>741</v>
       </c>
-      <c r="B95" s="1" t="s">
+      <c r="B96" s="1" t="s">
         <v>794</v>
       </c>
-      <c r="C95" s="1" t="s">
+      <c r="C96" s="1" t="s">
         <v>742</v>
       </c>
-      <c r="D95" s="1" t="s">
+      <c r="D96" s="1" t="s">
         <v>743</v>
       </c>
-      <c r="E95" s="1" t="s">
+      <c r="E96" s="1" t="s">
         <v>744</v>
       </c>
-      <c r="F95" s="1" t="s">
+      <c r="F96" s="1" t="s">
         <v>745</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A96" s="3"/>
-      <c r="B96" s="1"/>
-      <c r="C96" s="1"/>
-      <c r="D96" s="1"/>
-      <c r="E96" s="1"/>
-      <c r="F96" s="1"/>
-    </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A97" s="3" t="s">
-        <v>795</v>
-      </c>
-      <c r="B97" s="1" t="s">
-        <v>797</v>
-      </c>
-      <c r="C97" s="1" t="s">
-        <v>807</v>
-      </c>
-      <c r="D97" s="1" t="s">
-        <v>808</v>
-      </c>
-      <c r="E97" s="1" t="s">
-        <v>809</v>
-      </c>
-      <c r="F97" s="1" t="s">
-        <v>810</v>
-      </c>
+      <c r="A97" s="3"/>
+      <c r="B97" s="1"/>
+      <c r="C97" s="1"/>
+      <c r="D97" s="1"/>
+      <c r="E97" s="1"/>
+      <c r="F97" s="1"/>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
+        <v>795</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>797</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>807</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>808</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>809</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A99" s="3" t="s">
         <v>796</v>
       </c>
-      <c r="B98" s="1" t="s">
+      <c r="B99" s="1" t="s">
         <v>798</v>
       </c>
-      <c r="C98" s="1" t="s">
+      <c r="C99" s="1" t="s">
         <v>811</v>
       </c>
-      <c r="D98" s="1" t="s">
+      <c r="D99" s="1" t="s">
         <v>812</v>
       </c>
-      <c r="E98" s="1" t="s">
+      <c r="E99" s="1" t="s">
         <v>813</v>
       </c>
-      <c r="F98" s="1" t="s">
+      <c r="F99" s="1" t="s">
         <v>814</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A99" s="3"/>
-      <c r="B99" s="1"/>
-      <c r="C99" s="1"/>
-      <c r="D99" s="1"/>
-      <c r="E99" s="1"/>
-      <c r="F99" s="1"/>
-    </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A100" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="B100" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="C100" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="E100" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="F100" s="1" t="s">
-        <v>98</v>
-      </c>
+      <c r="A100" s="3"/>
+      <c r="B100" s="1"/>
+      <c r="C100" s="1"/>
+      <c r="D100" s="1"/>
+      <c r="E100" s="1"/>
+      <c r="F100" s="1"/>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A102" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="B101" s="1" t="s">
+      <c r="B102" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="C101" s="1" t="s">
+      <c r="C102" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="D101" s="1" t="s">
+      <c r="D102" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="E101" s="1" t="s">
+      <c r="E102" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="F101" s="1" t="s">
+      <c r="F102" s="1" t="s">
         <v>103</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A103" s="4" t="s">
-        <v>336</v>
-      </c>
-      <c r="B103" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="C103" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="D103" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="E103" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="F103" s="2" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>340</v>
-      </c>
-      <c r="B104" s="9" t="s">
-        <v>339</v>
+        <v>336</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>342</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="4" t="s">
-        <v>337</v>
-      </c>
-      <c r="B105" s="1" t="s">
-        <v>343</v>
+        <v>340</v>
+      </c>
+      <c r="B105" s="9" t="s">
+        <v>339</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="4" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>346</v>
-      </c>
-      <c r="B108" t="s">
-        <v>347</v>
+        <v>338</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>345</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="4" t="s">
-        <v>349</v>
-      </c>
-      <c r="B109" s="9" t="s">
-        <v>348</v>
+        <v>346</v>
+      </c>
+      <c r="B109" t="s">
+        <v>347</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>352</v>
-      </c>
-      <c r="B110" t="s">
-        <v>353</v>
+        <v>349</v>
+      </c>
+      <c r="B110" s="9" t="s">
+        <v>348</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="4" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B111" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="B112" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="B113" t="s">
+        <v>355</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="E113" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="F113" s="2" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A114" s="4" t="s">
         <v>357</v>
       </c>
-      <c r="B113" t="s">
+      <c r="B114" t="s">
         <v>356</v>
       </c>
-      <c r="C113" s="2" t="s">
+      <c r="C114" s="2" t="s">
         <v>397</v>
       </c>
-      <c r="D113" s="2" t="s">
+      <c r="D114" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="E113" s="2" t="s">
+      <c r="E114" s="2" t="s">
         <v>399</v>
       </c>
-      <c r="F113" s="2" t="s">
+      <c r="F114" s="2" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C114" s="2"/>
-      <c r="D114" s="2"/>
-      <c r="E114" s="2"/>
-      <c r="F114" s="2"/>
-    </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A115" s="4" t="s">
-        <v>747</v>
-      </c>
-      <c r="B115" t="s">
-        <v>746</v>
-      </c>
-      <c r="C115" t="s">
-        <v>750</v>
-      </c>
-      <c r="D115" t="s">
-        <v>751</v>
-      </c>
-      <c r="E115" t="s">
-        <v>752</v>
-      </c>
-      <c r="F115" t="s">
-        <v>753</v>
-      </c>
+      <c r="C115" s="2"/>
+      <c r="D115" s="2"/>
+      <c r="E115" s="2"/>
+      <c r="F115" s="2"/>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="B116" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="C116" t="s">
-        <v>754</v>
+        <v>750</v>
       </c>
       <c r="D116" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="E116" t="s">
-        <v>756</v>
+        <v>752</v>
       </c>
       <c r="F116" t="s">
-        <v>757</v>
+        <v>753</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="4" t="s">
+        <v>749</v>
+      </c>
+      <c r="B117" t="s">
+        <v>748</v>
+      </c>
+      <c r="C117" t="s">
+        <v>754</v>
+      </c>
+      <c r="D117" t="s">
+        <v>755</v>
+      </c>
+      <c r="E117" t="s">
+        <v>756</v>
+      </c>
+      <c r="F117" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A118" s="4" t="s">
         <v>760</v>
       </c>
-      <c r="B117" t="s">
+      <c r="B118" t="s">
         <v>759</v>
       </c>
-      <c r="C117" t="s">
+      <c r="C118" t="s">
         <v>758</v>
       </c>
-      <c r="D117" t="s">
+      <c r="D118" t="s">
         <v>761</v>
       </c>
-      <c r="E117" t="s">
+      <c r="E118" t="s">
         <v>762</v>
       </c>
-      <c r="F117" t="s">
+      <c r="F118" t="s">
         <v>763</v>
       </c>
     </row>
-    <row r="119" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="11" t="s">
+    <row r="120" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A120" s="11" t="s">
         <v>512</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A120" s="4" t="s">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A121" s="4" t="s">
         <v>471</v>
       </c>
-      <c r="B120" t="s">
+      <c r="B121" t="s">
         <v>472</v>
       </c>
-      <c r="C120" t="s">
+      <c r="C121" t="s">
         <v>473</v>
       </c>
-      <c r="D120" t="s">
+      <c r="D121" t="s">
         <v>474</v>
       </c>
-      <c r="E120" t="s">
+      <c r="E121" t="s">
         <v>473</v>
       </c>
-      <c r="F120" t="s">
+      <c r="F121" t="s">
         <v>475</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A121" s="5" t="s">
-        <v>476</v>
-      </c>
-      <c r="B121" t="s">
-        <v>548</v>
-      </c>
-      <c r="C121" t="s">
-        <v>477</v>
-      </c>
-      <c r="D121" t="s">
-        <v>478</v>
-      </c>
-      <c r="E121" t="s">
-        <v>479</v>
-      </c>
-      <c r="F121" t="s">
-        <v>480</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="5" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="B122" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C122" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="D122" t="s">
-        <v>513</v>
+        <v>478</v>
       </c>
       <c r="E122" t="s">
-        <v>524</v>
+        <v>479</v>
       </c>
       <c r="F122" t="s">
-        <v>534</v>
+        <v>480</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="5" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="B123" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C123" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="D123" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E123" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="F123" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="5" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="B124" t="s">
-        <v>486</v>
+        <v>550</v>
       </c>
       <c r="C124" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="D124" t="s">
-        <v>487</v>
+        <v>514</v>
       </c>
       <c r="E124" t="s">
-        <v>487</v>
+        <v>525</v>
       </c>
       <c r="F124" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="5" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="B125" t="s">
-        <v>551</v>
+        <v>486</v>
       </c>
       <c r="C125" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D125" t="s">
-        <v>515</v>
+        <v>487</v>
       </c>
       <c r="E125" t="s">
-        <v>526</v>
+        <v>487</v>
       </c>
       <c r="F125" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="5" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B126" t="s">
-        <v>494</v>
+        <v>551</v>
       </c>
       <c r="C126" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="D126" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="E126" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="F126" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="5" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B127" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C127" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D127" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="E127" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="F127" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="5" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="B128" t="s">
-        <v>552</v>
+        <v>495</v>
       </c>
       <c r="C128" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="D128" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E128" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="F128" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="5" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="B129" t="s">
-        <v>499</v>
+        <v>552</v>
       </c>
       <c r="C129" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="D129" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="E129" t="s">
-        <v>519</v>
+        <v>529</v>
       </c>
       <c r="F129" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="5" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="B130" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C130" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="D130" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="E130" t="s">
-        <v>530</v>
+        <v>519</v>
       </c>
       <c r="F130" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="5" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="B131" t="s">
-        <v>553</v>
+        <v>501</v>
       </c>
       <c r="C131" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="D131" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="E131" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="F131" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="5" t="s">
-        <v>546</v>
+        <v>504</v>
       </c>
       <c r="B132" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="C132" t="s">
-        <v>558</v>
+        <v>505</v>
       </c>
       <c r="D132" t="s">
-        <v>560</v>
+        <v>521</v>
       </c>
       <c r="E132" t="s">
-        <v>562</v>
+        <v>531</v>
       </c>
       <c r="F132" t="s">
-        <v>564</v>
+        <v>543</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="5" t="s">
+        <v>546</v>
+      </c>
+      <c r="B133" t="s">
+        <v>556</v>
+      </c>
+      <c r="C133" t="s">
+        <v>558</v>
+      </c>
+      <c r="D133" t="s">
+        <v>560</v>
+      </c>
+      <c r="E133" t="s">
+        <v>562</v>
+      </c>
+      <c r="F133" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A134" s="5" t="s">
         <v>547</v>
       </c>
-      <c r="B133" t="s">
+      <c r="B134" t="s">
         <v>557</v>
       </c>
-      <c r="C133" t="s">
+      <c r="C134" t="s">
         <v>559</v>
       </c>
-      <c r="D133" t="s">
+      <c r="D134" t="s">
         <v>561</v>
       </c>
-      <c r="E133" t="s">
+      <c r="E134" t="s">
         <v>563</v>
       </c>
-      <c r="F133" t="s">
+      <c r="F134" t="s">
         <v>565</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A134" s="4" t="s">
-        <v>506</v>
-      </c>
-      <c r="B134" t="s">
-        <v>554</v>
-      </c>
-      <c r="C134" t="s">
-        <v>566</v>
-      </c>
-      <c r="D134" t="s">
-        <v>567</v>
-      </c>
-      <c r="E134" t="s">
-        <v>568</v>
-      </c>
-      <c r="F134" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="4" t="s">
-        <v>618</v>
+        <v>506</v>
       </c>
       <c r="B135" t="s">
-        <v>619</v>
+        <v>554</v>
       </c>
       <c r="C135" t="s">
-        <v>620</v>
+        <v>566</v>
       </c>
       <c r="D135" t="s">
-        <v>621</v>
+        <v>567</v>
       </c>
       <c r="E135" t="s">
-        <v>622</v>
+        <v>568</v>
       </c>
       <c r="F135" t="s">
-        <v>623</v>
+        <v>569</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>507</v>
+        <v>618</v>
       </c>
       <c r="B136" t="s">
-        <v>555</v>
+        <v>619</v>
       </c>
       <c r="C136" t="s">
-        <v>508</v>
+        <v>620</v>
       </c>
       <c r="D136" t="s">
-        <v>522</v>
+        <v>621</v>
       </c>
       <c r="E136" t="s">
-        <v>532</v>
+        <v>622</v>
       </c>
       <c r="F136" t="s">
-        <v>544</v>
+        <v>623</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="4" t="s">
+        <v>507</v>
+      </c>
+      <c r="B137" t="s">
+        <v>555</v>
+      </c>
+      <c r="C137" t="s">
+        <v>508</v>
+      </c>
+      <c r="D137" t="s">
+        <v>522</v>
+      </c>
+      <c r="E137" t="s">
+        <v>532</v>
+      </c>
+      <c r="F137" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A138" s="4" t="s">
         <v>509</v>
       </c>
-      <c r="B137" t="s">
+      <c r="B138" t="s">
         <v>510</v>
       </c>
-      <c r="C137" t="s">
+      <c r="C138" t="s">
         <v>511</v>
       </c>
-      <c r="D137" t="s">
+      <c r="D138" t="s">
         <v>523</v>
       </c>
-      <c r="E137" t="s">
+      <c r="E138" t="s">
         <v>533</v>
       </c>
-      <c r="F137" t="s">
+      <c r="F138" t="s">
         <v>545</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A139" s="4" t="s">
-        <v>575</v>
-      </c>
-      <c r="B139" t="s">
-        <v>574</v>
-      </c>
-      <c r="C139" t="s">
-        <v>570</v>
-      </c>
-      <c r="D139" t="s">
-        <v>571</v>
-      </c>
-      <c r="E139" t="s">
-        <v>572</v>
-      </c>
-      <c r="F139" t="s">
-        <v>573</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B140" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="C140" t="s">
-        <v>578</v>
+        <v>570</v>
       </c>
       <c r="D140" t="s">
-        <v>579</v>
+        <v>571</v>
       </c>
       <c r="E140" t="s">
-        <v>580</v>
+        <v>572</v>
       </c>
       <c r="F140" t="s">
-        <v>581</v>
+        <v>573</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="4" t="s">
-        <v>582</v>
+        <v>576</v>
       </c>
       <c r="B141" t="s">
-        <v>583</v>
+        <v>577</v>
       </c>
       <c r="C141" t="s">
-        <v>584</v>
+        <v>578</v>
       </c>
       <c r="D141" t="s">
-        <v>585</v>
+        <v>579</v>
       </c>
       <c r="E141" t="s">
-        <v>586</v>
+        <v>580</v>
       </c>
       <c r="F141" t="s">
-        <v>587</v>
+        <v>581</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>589</v>
+        <v>582</v>
       </c>
       <c r="B142" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
       <c r="C142" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
       <c r="D142" t="s">
-        <v>591</v>
+        <v>585</v>
       </c>
       <c r="E142" t="s">
-        <v>592</v>
+        <v>586</v>
       </c>
       <c r="F142" t="s">
-        <v>593</v>
+        <v>587</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="4" t="s">
-        <v>595</v>
+        <v>589</v>
       </c>
       <c r="B143" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
       <c r="C143" t="s">
-        <v>596</v>
+        <v>590</v>
       </c>
       <c r="D143" t="s">
-        <v>597</v>
+        <v>591</v>
       </c>
       <c r="E143" t="s">
-        <v>598</v>
+        <v>592</v>
       </c>
       <c r="F143" t="s">
-        <v>599</v>
+        <v>593</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="B144" t="s">
-        <v>603</v>
+        <v>594</v>
       </c>
       <c r="C144" t="s">
-        <v>604</v>
+        <v>596</v>
       </c>
       <c r="D144" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="E144" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="F144" t="s">
-        <v>607</v>
+        <v>599</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="4" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B145" t="s">
-        <v>608</v>
+        <v>603</v>
       </c>
       <c r="C145" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="D145" t="s">
-        <v>610</v>
+        <v>605</v>
       </c>
       <c r="E145" t="s">
-        <v>611</v>
+        <v>606</v>
       </c>
       <c r="F145" t="s">
-        <v>612</v>
+        <v>607</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
+        <v>601</v>
+      </c>
+      <c r="B146" t="s">
+        <v>608</v>
+      </c>
+      <c r="C146" t="s">
+        <v>609</v>
+      </c>
+      <c r="D146" t="s">
+        <v>610</v>
+      </c>
+      <c r="E146" t="s">
+        <v>611</v>
+      </c>
+      <c r="F146" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A147" s="4" t="s">
         <v>602</v>
       </c>
-      <c r="B146" t="s">
+      <c r="B147" t="s">
         <v>613</v>
       </c>
-      <c r="C146" t="s">
+      <c r="C147" t="s">
         <v>614</v>
       </c>
-      <c r="D146" t="s">
+      <c r="D147" t="s">
         <v>615</v>
       </c>
-      <c r="E146" t="s">
+      <c r="E147" t="s">
         <v>616</v>
       </c>
-      <c r="F146" t="s">
+      <c r="F147" t="s">
         <v>617</v>
-      </c>
-    </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A148" s="4" t="s">
-        <v>729</v>
-      </c>
-      <c r="B148" t="s">
-        <v>679</v>
-      </c>
-      <c r="C148" t="s">
-        <v>680</v>
-      </c>
-      <c r="D148" t="s">
-        <v>681</v>
-      </c>
-      <c r="E148" t="s">
-        <v>682</v>
-      </c>
-      <c r="F148" t="s">
-        <v>683</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="4" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B149" t="s">
-        <v>724</v>
+        <v>679</v>
       </c>
       <c r="C149" t="s">
-        <v>725</v>
+        <v>680</v>
       </c>
       <c r="D149" t="s">
-        <v>726</v>
+        <v>681</v>
       </c>
       <c r="E149" t="s">
-        <v>727</v>
+        <v>682</v>
       </c>
       <c r="F149" t="s">
-        <v>728</v>
+        <v>683</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B150" t="s">
-        <v>690</v>
+        <v>724</v>
       </c>
       <c r="C150" t="s">
-        <v>691</v>
+        <v>725</v>
       </c>
       <c r="D150" t="s">
-        <v>692</v>
+        <v>726</v>
       </c>
       <c r="E150" t="s">
-        <v>693</v>
+        <v>727</v>
       </c>
       <c r="F150" t="s">
-        <v>694</v>
+        <v>728</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="4" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="B151" t="s">
-        <v>719</v>
+        <v>690</v>
       </c>
       <c r="C151" t="s">
-        <v>720</v>
+        <v>691</v>
       </c>
       <c r="D151" t="s">
-        <v>721</v>
+        <v>692</v>
       </c>
       <c r="E151" t="s">
-        <v>722</v>
+        <v>693</v>
       </c>
       <c r="F151" t="s">
-        <v>723</v>
+        <v>694</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B152" t="s">
-        <v>684</v>
+        <v>719</v>
       </c>
       <c r="C152" t="s">
-        <v>685</v>
+        <v>720</v>
       </c>
       <c r="D152" t="s">
-        <v>686</v>
+        <v>721</v>
       </c>
       <c r="E152" t="s">
-        <v>687</v>
+        <v>722</v>
       </c>
       <c r="F152" t="s">
-        <v>688</v>
+        <v>723</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="4" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B153" t="s">
-        <v>714</v>
+        <v>684</v>
       </c>
       <c r="C153" t="s">
-        <v>715</v>
+        <v>685</v>
       </c>
       <c r="D153" t="s">
-        <v>716</v>
+        <v>686</v>
       </c>
       <c r="E153" t="s">
-        <v>717</v>
+        <v>687</v>
       </c>
       <c r="F153" t="s">
-        <v>718</v>
+        <v>688</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="B154" t="s">
-        <v>689</v>
+        <v>714</v>
       </c>
       <c r="C154" t="s">
-        <v>695</v>
+        <v>715</v>
       </c>
       <c r="D154" t="s">
-        <v>696</v>
+        <v>716</v>
       </c>
       <c r="E154" t="s">
-        <v>697</v>
+        <v>717</v>
       </c>
       <c r="F154" t="s">
-        <v>698</v>
+        <v>718</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="4" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B155" t="s">
-        <v>709</v>
+        <v>689</v>
       </c>
       <c r="C155" t="s">
-        <v>710</v>
+        <v>695</v>
       </c>
       <c r="D155" t="s">
-        <v>711</v>
+        <v>696</v>
       </c>
       <c r="E155" t="s">
-        <v>712</v>
+        <v>697</v>
       </c>
       <c r="F155" t="s">
-        <v>713</v>
+        <v>698</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="B156" t="s">
-        <v>699</v>
+        <v>709</v>
       </c>
       <c r="C156" t="s">
-        <v>700</v>
+        <v>710</v>
       </c>
       <c r="D156" t="s">
-        <v>701</v>
+        <v>711</v>
       </c>
       <c r="E156" t="s">
-        <v>702</v>
+        <v>712</v>
       </c>
       <c r="F156" t="s">
-        <v>703</v>
+        <v>713</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="4" t="s">
+        <v>737</v>
+      </c>
+      <c r="B157" t="s">
+        <v>699</v>
+      </c>
+      <c r="C157" t="s">
+        <v>700</v>
+      </c>
+      <c r="D157" t="s">
+        <v>701</v>
+      </c>
+      <c r="E157" t="s">
+        <v>702</v>
+      </c>
+      <c r="F157" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A158" s="4" t="s">
         <v>738</v>
       </c>
-      <c r="B157" t="s">
+      <c r="B158" t="s">
         <v>704</v>
       </c>
-      <c r="C157" t="s">
+      <c r="C158" t="s">
         <v>705</v>
       </c>
-      <c r="D157" t="s">
+      <c r="D158" t="s">
         <v>706</v>
       </c>
-      <c r="E157" t="s">
+      <c r="E158" t="s">
         <v>707</v>
       </c>
-      <c r="F157" t="s">
+      <c r="F158" t="s">
         <v>708</v>
       </c>
     </row>
-    <row r="159" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A159" s="11" t="s">
+    <row r="160" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A160" s="11" t="s">
         <v>815</v>
-      </c>
-    </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A160" s="4" t="s">
-        <v>642</v>
-      </c>
-      <c r="B160" t="s">
-        <v>740</v>
-      </c>
-      <c r="C160" t="s">
-        <v>624</v>
-      </c>
-      <c r="D160" t="s">
-        <v>625</v>
-      </c>
-      <c r="E160" t="s">
-        <v>626</v>
-      </c>
-      <c r="F160" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="4" t="s">
-        <v>678</v>
+        <v>642</v>
       </c>
       <c r="B161" t="s">
-        <v>673</v>
+        <v>740</v>
       </c>
       <c r="C161" t="s">
-        <v>674</v>
+        <v>624</v>
       </c>
       <c r="D161" t="s">
-        <v>675</v>
+        <v>625</v>
       </c>
       <c r="E161" t="s">
-        <v>676</v>
+        <v>626</v>
       </c>
       <c r="F161" t="s">
-        <v>677</v>
+        <v>627</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="s">
-        <v>643</v>
+        <v>678</v>
       </c>
       <c r="B162" t="s">
-        <v>739</v>
+        <v>673</v>
       </c>
       <c r="C162" t="s">
-        <v>638</v>
+        <v>674</v>
       </c>
       <c r="D162" t="s">
-        <v>639</v>
+        <v>675</v>
       </c>
       <c r="E162" t="s">
-        <v>640</v>
+        <v>676</v>
       </c>
       <c r="F162" t="s">
-        <v>641</v>
+        <v>677</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="4" t="s">
-        <v>649</v>
+        <v>643</v>
       </c>
       <c r="B163" t="s">
-        <v>644</v>
+        <v>739</v>
       </c>
       <c r="C163" t="s">
-        <v>645</v>
+        <v>638</v>
       </c>
       <c r="D163" t="s">
-        <v>646</v>
+        <v>639</v>
       </c>
       <c r="E163" t="s">
-        <v>647</v>
+        <v>640</v>
       </c>
       <c r="F163" t="s">
-        <v>648</v>
+        <v>641</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="4" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B164" t="s">
-        <v>651</v>
+        <v>644</v>
       </c>
       <c r="C164" t="s">
-        <v>658</v>
+        <v>645</v>
       </c>
       <c r="D164" t="s">
-        <v>659</v>
+        <v>646</v>
       </c>
       <c r="E164" t="s">
-        <v>659</v>
+        <v>647</v>
       </c>
       <c r="F164" t="s">
-        <v>666</v>
+        <v>648</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="4" t="s">
-        <v>668</v>
+        <v>650</v>
       </c>
       <c r="B165" t="s">
-        <v>667</v>
+        <v>651</v>
       </c>
       <c r="C165" t="s">
-        <v>669</v>
+        <v>658</v>
       </c>
       <c r="D165" t="s">
-        <v>670</v>
+        <v>659</v>
       </c>
       <c r="E165" t="s">
-        <v>671</v>
+        <v>659</v>
       </c>
       <c r="F165" t="s">
-        <v>672</v>
+        <v>666</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="4" t="s">
-        <v>771</v>
+        <v>668</v>
       </c>
       <c r="B166" t="s">
-        <v>768</v>
+        <v>667</v>
       </c>
       <c r="C166" t="s">
-        <v>772</v>
+        <v>669</v>
       </c>
       <c r="D166" t="s">
-        <v>773</v>
+        <v>670</v>
       </c>
       <c r="E166" t="s">
-        <v>774</v>
+        <v>671</v>
       </c>
       <c r="F166" t="s">
-        <v>775</v>
+        <v>672</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="4" t="s">
-        <v>652</v>
+        <v>771</v>
       </c>
       <c r="B167" t="s">
-        <v>653</v>
+        <v>768</v>
       </c>
       <c r="C167" t="s">
-        <v>654</v>
+        <v>772</v>
       </c>
       <c r="D167" t="s">
-        <v>655</v>
+        <v>773</v>
       </c>
       <c r="E167" t="s">
-        <v>656</v>
+        <v>774</v>
       </c>
       <c r="F167" t="s">
-        <v>657</v>
+        <v>775</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
-        <v>661</v>
+        <v>652</v>
       </c>
       <c r="B168" t="s">
-        <v>660</v>
+        <v>653</v>
       </c>
       <c r="C168" t="s">
-        <v>662</v>
+        <v>654</v>
       </c>
       <c r="D168" t="s">
-        <v>663</v>
+        <v>655</v>
       </c>
       <c r="E168" t="s">
-        <v>664</v>
+        <v>656</v>
       </c>
       <c r="F168" t="s">
-        <v>665</v>
+        <v>657</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="4" t="s">
-        <v>770</v>
+        <v>661</v>
       </c>
       <c r="B169" t="s">
-        <v>769</v>
+        <v>660</v>
       </c>
       <c r="C169" t="s">
-        <v>776</v>
+        <v>662</v>
       </c>
       <c r="D169" t="s">
-        <v>777</v>
+        <v>663</v>
       </c>
       <c r="E169" t="s">
-        <v>778</v>
+        <v>664</v>
       </c>
       <c r="F169" t="s">
-        <v>779</v>
+        <v>665</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="4" t="s">
-        <v>764</v>
+        <v>770</v>
       </c>
       <c r="B170" t="s">
-        <v>766</v>
+        <v>769</v>
       </c>
       <c r="C170" t="s">
-        <v>780</v>
+        <v>776</v>
       </c>
       <c r="D170" t="s">
-        <v>781</v>
+        <v>777</v>
       </c>
       <c r="E170" t="s">
-        <v>782</v>
+        <v>778</v>
       </c>
       <c r="F170" t="s">
-        <v>783</v>
+        <v>779</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="4" t="s">
+        <v>764</v>
+      </c>
+      <c r="B171" t="s">
+        <v>766</v>
+      </c>
+      <c r="C171" t="s">
+        <v>780</v>
+      </c>
+      <c r="D171" t="s">
+        <v>781</v>
+      </c>
+      <c r="E171" t="s">
+        <v>782</v>
+      </c>
+      <c r="F171" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A172" s="4" t="s">
         <v>765</v>
       </c>
-      <c r="B171" t="s">
+      <c r="B172" t="s">
         <v>767</v>
       </c>
-      <c r="C171" t="s">
+      <c r="C172" t="s">
         <v>784</v>
       </c>
-      <c r="D171" t="s">
+      <c r="D172" t="s">
         <v>785</v>
       </c>
-      <c r="E171" t="s">
+      <c r="E172" t="s">
         <v>786</v>
       </c>
-      <c r="F171" t="s">
+      <c r="F172" t="s">
         <v>787</v>
       </c>
     </row>
-    <row r="173" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A173" s="11" t="s">
+    <row r="174" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A174" s="11" t="s">
         <v>823</v>
-      </c>
-    </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A174" s="4" t="s">
-        <v>847</v>
-      </c>
-      <c r="B174" t="s">
-        <v>816</v>
-      </c>
-      <c r="C174" t="s">
-        <v>822</v>
-      </c>
-      <c r="D174" t="s">
-        <v>824</v>
-      </c>
-      <c r="E174" t="s">
-        <v>825</v>
-      </c>
-      <c r="F174" t="s">
-        <v>826</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="4" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="B175" t="s">
-        <v>845</v>
+        <v>816</v>
       </c>
       <c r="C175" t="s">
-        <v>849</v>
+        <v>822</v>
       </c>
       <c r="D175" t="s">
-        <v>850</v>
+        <v>824</v>
       </c>
       <c r="E175" t="s">
-        <v>851</v>
+        <v>825</v>
       </c>
       <c r="F175" t="s">
-        <v>852</v>
+        <v>826</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="4" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="B176" t="s">
-        <v>820</v>
+        <v>845</v>
       </c>
       <c r="C176" t="s">
-        <v>827</v>
+        <v>849</v>
       </c>
       <c r="D176" t="s">
-        <v>828</v>
+        <v>850</v>
       </c>
       <c r="E176" t="s">
-        <v>829</v>
+        <v>851</v>
       </c>
       <c r="F176" t="s">
-        <v>830</v>
+        <v>852</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="4" t="s">
-        <v>853</v>
+        <v>848</v>
       </c>
       <c r="B177" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="C177" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
       <c r="D177" t="s">
-        <v>832</v>
+        <v>828</v>
       </c>
       <c r="E177" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="F177" t="s">
-        <v>834</v>
+        <v>830</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="4" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B178" t="s">
-        <v>817</v>
+        <v>821</v>
       </c>
       <c r="C178" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="D178" t="s">
-        <v>836</v>
+        <v>832</v>
       </c>
       <c r="E178" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="F178" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="4" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="B179" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="C179" t="s">
-        <v>838</v>
+        <v>835</v>
       </c>
       <c r="D179" t="s">
-        <v>839</v>
+        <v>836</v>
       </c>
       <c r="E179" t="s">
-        <v>840</v>
+        <v>835</v>
       </c>
       <c r="F179" t="s">
-        <v>841</v>
+        <v>837</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="4" t="s">
+        <v>855</v>
+      </c>
+      <c r="B180" t="s">
+        <v>818</v>
+      </c>
+      <c r="C180" t="s">
+        <v>838</v>
+      </c>
+      <c r="D180" t="s">
+        <v>839</v>
+      </c>
+      <c r="E180" t="s">
+        <v>840</v>
+      </c>
+      <c r="F180" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A181" s="4" t="s">
         <v>856</v>
       </c>
-      <c r="B180" t="s">
+      <c r="B181" t="s">
         <v>819</v>
       </c>
-      <c r="C180" t="s">
+      <c r="C181" t="s">
         <v>842</v>
       </c>
-      <c r="D180" t="s">
+      <c r="D181" t="s">
         <v>843</v>
       </c>
-      <c r="E180" t="s">
+      <c r="E181" t="s">
         <v>843</v>
       </c>
-      <c r="F180" t="s">
+      <c r="F181" t="s">
         <v>844</v>
       </c>
     </row>
